--- a/office/office-claude/templates/TC_template.xlsx
+++ b/office/office-claude/templates/TC_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuya_\claude\office\office-claude\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1741BA57-48EA-4C58-B17F-9B9F0815ED13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1FD3F0-B760-4A43-83F4-BAFF4BE1606A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="756" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="278">
   <si>
     <t>テンプレート用サンプル株式会社 消費税区分チェックレポート</t>
   </si>
@@ -634,6 +634,12 @@
     <t>住宅家賃（支払）が課税</t>
   </si>
   <si>
+    <t>駐車場・付随設備の判定要確認</t>
+  </si>
+  <si>
+    <t>駐車場判定要確認</t>
+  </si>
+  <si>
     <t>受取家賃が非課売上 + 事業用KW</t>
   </si>
   <si>
@@ -730,6 +736,9 @@
     <t>損害賠償金の課税性確認</t>
   </si>
   <si>
+    <t>損害賠償は要確認</t>
+  </si>
+  <si>
     <t>雑収入でKWマッチ</t>
   </si>
   <si>
@@ -784,6 +793,18 @@
     <t>租税公課は非課OK</t>
   </si>
   <si>
+    <t>軽油引取税の判定要確認 (V1-3-30へ)</t>
+  </si>
+  <si>
+    <t>軽油引取税は要確認</t>
+  </si>
+  <si>
+    <t>ゴルフ場利用税・入湯税の判定要確認</t>
+  </si>
+  <si>
+    <t>ゴルフ・入湯税は要確認</t>
+  </si>
+  <si>
     <t>慶弔見舞金が課税仕入 (Conf: 90)</t>
   </si>
   <si>
@@ -818,56 +839,6 @@
   </si>
   <si>
     <t>食品なのに10%</t>
-  </si>
-  <si>
-    <t>A14 インボイス</t>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>A14</t>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>インボイス</t>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>参考</t>
-  </si>
-  <si>
-    <t>参考</t>
-    <rPh sb="0" eb="2">
-      <t>サンコウ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>要確認</t>
-    <rPh sb="0" eb="3">
-      <t>ヨウカクニン</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>要修正</t>
-  </si>
-  <si>
-    <t>要修正</t>
-    <rPh sb="0" eb="3">
-      <t>ヨウシュウセイ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>要判断</t>
-  </si>
-  <si>
-    <t>念のため事実関係の再確認を推奨</t>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>影響は軽微、表示形式等の整合性に関する通知</t>
-    <phoneticPr fontId="6"/>
   </si>
   <si>
     <t>要修正（必須）</t>
@@ -893,6 +864,20 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
+    <t>要確認（推奨）</t>
+    <rPh sb="0" eb="3">
+      <t>ヨウカクニン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>スイショウ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>念のため事実関係の再確認を推奨</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
     <t>参考（任意）</t>
     <rPh sb="0" eb="2">
       <t>サンコウ</t>
@@ -903,6 +888,17 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
+    <t>影響は軽微、表示形式等の整合性に関する通知</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>要修正</t>
+    <rPh sb="0" eb="3">
+      <t>ヨウシュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
     <t>要判断</t>
     <rPh sb="0" eb="3">
       <t>ヨウハンダン</t>
@@ -910,52 +906,37 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>駐車場・付随設備の判定参考</t>
-  </si>
-  <si>
-    <t>駐車場判定参考</t>
-  </si>
-  <si>
-    <t>損害賠償は参考</t>
-  </si>
-  <si>
-    <t>軽油引取税の判定参考 (V1-3-30へ)</t>
-  </si>
-  <si>
-    <t>軽油引取税は参考</t>
-  </si>
-  <si>
-    <t>ゴルフ場利用税・入湯税の判定参考</t>
-  </si>
-  <si>
-    <t>ゴルフ・入湯税は参考</t>
-  </si>
-  <si>
-    <t>TC-INV</t>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>インボイス適格/非適格など</t>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>インボイス適格/非適格など</t>
-    <rPh sb="5" eb="7">
-      <t>テキカク</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>ヒテキカク</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>要確認（推奨）</t>
+    <t>要確認</t>
     <rPh sb="0" eb="3">
       <t>ヨウカクニン</t>
     </rPh>
-    <rPh sb="4" eb="6">
-      <t>スイショウ</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>参考</t>
+    <rPh sb="0" eb="2">
+      <t>サンコウ</t>
     </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>TC-INV</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>インボイス適格/非適格など</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>A14</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>インボイス</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>A14 インボイス</t>
     <phoneticPr fontId="6"/>
   </si>
 </sst>
@@ -1044,7 +1025,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1112,18 +1093,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFAEEDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF5D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF3DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDD9"/>
-        <bgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1181,6 +1171,51 @@
       <right style="thin">
         <color rgb="FFD9D9D9"/>
       </right>
+      <top style="medium">
+        <color rgb="FFED7D31"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFED7D31"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFBF8F00"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBF8F00"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF548235"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF548235"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
       <top style="thin">
         <color rgb="FFD9D9D9"/>
       </top>
@@ -1190,19 +1225,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="4">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="5">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="6">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1218,7 +1260,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1231,9 +1272,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1289,13 +1327,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="55" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1305,34 +1339,119 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="4" xfId="2">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="4" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="5" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="5">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="6" xfId="4">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="5" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="5" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="6" xfId="4" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="5" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="4" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="5" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="6" xfId="4" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="5" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="4" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="5" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="6" xfId="4" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="55" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="child_row_style" xfId="2" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+  <cellStyles count="6">
+    <cellStyle name="child_row_style" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
     <cellStyle name="parent_row_style_critical" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="parent_row_style_low" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="parent_row_style_medium" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="parent_row_style_warning" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFFEFDD9"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1632,640 +1751,653 @@
   <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="13" width="10.625" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="36.625" customWidth="1"/>
+    <col min="1" max="1" width="10" style="15" customWidth="1"/>
+    <col min="2" max="13" width="10.625" style="15" customWidth="1"/>
+    <col min="14" max="14" width="14" style="15" customWidth="1"/>
+    <col min="15" max="15" width="36.625" style="15" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N2" s="8" t="s">
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="N2" s="62" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="16" t="s">
+      <c r="N3" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="64">
+        <v>45992</v>
+      </c>
+      <c r="N4" s="60" t="s">
+        <v>264</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="61">
+        <v>46150</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="N6" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O6" s="6" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="65" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+    </row>
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="66"/>
+      <c r="D9" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E9" s="60" t="s">
+        <v>270</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="66"/>
+      <c r="D10" s="8">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1</v>
+      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8">
+        <v>1</v>
+      </c>
+      <c r="H10" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="66"/>
+      <c r="D11" s="8">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1</v>
+      </c>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="66"/>
+      <c r="D12" s="8">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8">
+        <v>1</v>
+      </c>
+      <c r="H12" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="66"/>
+      <c r="D13" s="8">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1</v>
+      </c>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="66"/>
+      <c r="D14" s="8">
+        <v>1</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1</v>
+      </c>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8">
+        <v>1</v>
+      </c>
+      <c r="H14" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="66"/>
+      <c r="D15" s="8">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="66"/>
+      <c r="D16" s="8">
+        <v>0</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8">
+        <v>1</v>
+      </c>
+      <c r="H16" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>274</v>
+      </c>
+      <c r="C17" s="66"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+    </row>
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="31"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="9">
+        <v>6</v>
+      </c>
+      <c r="E18" s="9">
+        <v>7</v>
+      </c>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="33">
-        <v>45992</v>
-      </c>
-      <c r="N4" s="39" t="s">
-        <v>268</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="40">
-        <v>46150</v>
-      </c>
-      <c r="N5" s="17" t="s">
-        <v>281</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="N6" s="18" t="s">
+      <c r="H18" s="9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="66"/>
+      <c r="D21" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="33"/>
+      <c r="G21" s="66"/>
+      <c r="H21" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="O6" s="9" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-    </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="E9" s="39" t="s">
+      <c r="J21" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="34" t="s">
+      <c r="K21" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="O21" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="66"/>
+      <c r="D22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="34"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="10">
+        <v>2</v>
+      </c>
+      <c r="I22" s="10">
+        <v>1</v>
+      </c>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10">
+        <v>1</v>
+      </c>
+      <c r="L22" s="10">
+        <v>0</v>
+      </c>
+      <c r="M22" s="10">
+        <v>2</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="O22" s="11"/>
+    </row>
+    <row r="23" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="66"/>
+      <c r="D23" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="34"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="10">
+        <v>3</v>
+      </c>
+      <c r="I23" s="10">
+        <v>1</v>
+      </c>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10">
+        <v>1</v>
+      </c>
+      <c r="L23" s="10">
+        <v>1</v>
+      </c>
+      <c r="M23" s="10">
+        <v>3</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="O23" s="11"/>
+    </row>
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="66"/>
+      <c r="D24" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="34"/>
+      <c r="G24" s="66"/>
+      <c r="H24" s="10">
+        <v>2</v>
+      </c>
+      <c r="I24" s="10">
+        <v>0</v>
+      </c>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10">
+        <v>1</v>
+      </c>
+      <c r="L24" s="10">
+        <v>1</v>
+      </c>
+      <c r="M24" s="10">
+        <v>2</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="O24" s="11"/>
+    </row>
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="66"/>
+      <c r="D25" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="11">
+      <c r="F25" s="34"/>
+      <c r="G25" s="66"/>
+      <c r="H25" s="10">
+        <v>3</v>
+      </c>
+      <c r="I25" s="10">
         <v>1</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11">
+      <c r="J25" s="10"/>
+      <c r="K25" s="10">
         <v>1</v>
       </c>
-      <c r="G10" s="11">
+      <c r="L25" s="10">
         <v>1</v>
       </c>
-      <c r="H10" s="11">
+      <c r="M25" s="10">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="11">
+      <c r="N25" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="O25" s="11"/>
+    </row>
+    <row r="26" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="66"/>
+      <c r="D26" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="34"/>
+      <c r="G26" s="66"/>
+      <c r="H26" s="10">
+        <v>3</v>
+      </c>
+      <c r="I26" s="10">
         <v>1</v>
       </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11">
+      <c r="J26" s="10"/>
+      <c r="K26" s="10">
         <v>1</v>
       </c>
-      <c r="G11" s="11">
+      <c r="L26" s="10">
+        <v>1</v>
+      </c>
+      <c r="M26" s="10">
+        <v>3</v>
+      </c>
+      <c r="N26" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="O26" s="11"/>
+    </row>
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="66"/>
+      <c r="D27" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E27" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" s="34"/>
+      <c r="G27" s="66"/>
+      <c r="H27" s="10">
+        <v>2</v>
+      </c>
+      <c r="I27" s="10">
+        <v>1</v>
+      </c>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10">
+        <v>1</v>
+      </c>
+      <c r="L27" s="10">
         <v>0</v>
       </c>
-      <c r="H11" s="11">
+      <c r="M27" s="10">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="11">
+      <c r="N27" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="O27" s="11"/>
+    </row>
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="66"/>
+      <c r="D28" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="34"/>
+      <c r="G28" s="66"/>
+      <c r="H28" s="10">
+        <v>2</v>
+      </c>
+      <c r="I28" s="10">
         <v>1</v>
       </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11">
+      <c r="J28" s="10"/>
+      <c r="K28" s="10">
         <v>1</v>
       </c>
-      <c r="G12" s="11">
+      <c r="L28" s="10">
+        <v>0</v>
+      </c>
+      <c r="M28" s="10">
+        <v>2</v>
+      </c>
+      <c r="N28" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="O28" s="11"/>
+    </row>
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B29" s="29" t="s">
+        <v>276</v>
+      </c>
+      <c r="C29" s="66"/>
+      <c r="D29" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E29" s="29" t="s">
+        <v>274</v>
+      </c>
+      <c r="F29" s="34"/>
+      <c r="G29" s="66"/>
+      <c r="H29" s="10">
+        <v>2</v>
+      </c>
+      <c r="I29" s="10">
         <v>1</v>
       </c>
-      <c r="H12" s="11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="35"/>
-      <c r="D13" s="11">
+      <c r="J29" s="10"/>
+      <c r="K29" s="10">
         <v>1</v>
       </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11">
-        <v>1</v>
-      </c>
-      <c r="G13" s="11">
+      <c r="L29" s="10">
         <v>0</v>
       </c>
-      <c r="H13" s="11">
+      <c r="M29" s="10">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="11">
-        <v>1</v>
-      </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11">
-        <v>1</v>
-      </c>
-      <c r="G14" s="11">
-        <v>1</v>
-      </c>
-      <c r="H14" s="11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="35"/>
-      <c r="D15" s="11">
-        <v>1</v>
-      </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11">
-        <v>1</v>
-      </c>
-      <c r="G15" s="11">
-        <v>0</v>
-      </c>
-      <c r="H15" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="35"/>
-      <c r="D16" s="11">
-        <v>0</v>
-      </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11">
-        <v>1</v>
-      </c>
-      <c r="G16" s="11">
-        <v>1</v>
-      </c>
-      <c r="H16" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="B17" s="34" t="s">
-        <v>279</v>
-      </c>
-      <c r="C17" s="35"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-    </row>
-    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="12">
-        <v>6</v>
-      </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12">
-        <v>7</v>
-      </c>
-      <c r="G18" s="12">
-        <v>4</v>
-      </c>
-      <c r="H18" s="12">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="35"/>
-      <c r="D21" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="10"/>
-      <c r="F21" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="35"/>
-      <c r="H21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="J21" s="39" t="s">
-        <v>270</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="L21" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="M21" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="N21" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="O21" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="35"/>
-      <c r="H22" s="14">
-        <v>2</v>
-      </c>
-      <c r="I22" s="14">
-        <v>1</v>
-      </c>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14">
-        <v>1</v>
-      </c>
-      <c r="L22" s="14">
-        <v>0</v>
-      </c>
-      <c r="M22" s="14">
-        <v>2</v>
-      </c>
-      <c r="N22" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O22" s="15"/>
-    </row>
-    <row r="23" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" s="35"/>
-      <c r="D23" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="11"/>
-      <c r="F23" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" s="35"/>
-      <c r="H23" s="14">
-        <v>3</v>
-      </c>
-      <c r="I23" s="14">
-        <v>1</v>
-      </c>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14">
-        <v>1</v>
-      </c>
-      <c r="L23" s="14">
-        <v>1</v>
-      </c>
-      <c r="M23" s="14">
-        <v>3</v>
-      </c>
-      <c r="N23" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O23" s="15"/>
-    </row>
-    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="11"/>
-      <c r="F24" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24" s="35"/>
-      <c r="H24" s="14">
-        <v>2</v>
-      </c>
-      <c r="I24" s="14">
-        <v>0</v>
-      </c>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14">
-        <v>1</v>
-      </c>
-      <c r="L24" s="14">
-        <v>1</v>
-      </c>
-      <c r="M24" s="14">
-        <v>2</v>
-      </c>
-      <c r="N24" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O24" s="15"/>
-    </row>
-    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E25" s="11"/>
-      <c r="F25" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="35"/>
-      <c r="H25" s="14">
-        <v>3</v>
-      </c>
-      <c r="I25" s="14">
-        <v>1</v>
-      </c>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14">
-        <v>1</v>
-      </c>
-      <c r="L25" s="14">
-        <v>1</v>
-      </c>
-      <c r="M25" s="14">
-        <v>3</v>
-      </c>
-      <c r="N25" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O25" s="15"/>
-    </row>
-    <row r="26" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" s="11"/>
-      <c r="F26" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" s="35"/>
-      <c r="H26" s="14">
-        <v>3</v>
-      </c>
-      <c r="I26" s="14">
-        <v>1</v>
-      </c>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14">
-        <v>1</v>
-      </c>
-      <c r="L26" s="14">
-        <v>1</v>
-      </c>
-      <c r="M26" s="14">
-        <v>3</v>
-      </c>
-      <c r="N26" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O26" s="15"/>
-    </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="35"/>
-      <c r="D27" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E27" s="11"/>
-      <c r="F27" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" s="35"/>
-      <c r="H27" s="14">
-        <v>2</v>
-      </c>
-      <c r="I27" s="14">
-        <v>1</v>
-      </c>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14">
-        <v>1</v>
-      </c>
-      <c r="L27" s="14">
-        <v>0</v>
-      </c>
-      <c r="M27" s="14">
-        <v>2</v>
-      </c>
-      <c r="N27" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O27" s="15"/>
-    </row>
-    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="35"/>
-      <c r="D28" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E28" s="11"/>
-      <c r="F28" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="G28" s="35"/>
-      <c r="H28" s="14">
-        <v>2</v>
-      </c>
-      <c r="I28" s="14">
-        <v>1</v>
-      </c>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14">
-        <v>1</v>
-      </c>
-      <c r="L28" s="14">
-        <v>0</v>
-      </c>
-      <c r="M28" s="14">
-        <v>2</v>
-      </c>
-      <c r="N28" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O28" s="15"/>
-    </row>
-    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B29" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="C29" s="35"/>
-      <c r="D29" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="E29" s="11"/>
-      <c r="F29" s="34" t="s">
-        <v>280</v>
-      </c>
-      <c r="G29" s="35"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="15"/>
+      <c r="N29" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="O29" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="28">
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="E29:G29"/>
     <mergeCell ref="B10:C10"/>
-    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="E28:G28"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="E27:G27"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="E26:G26"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="E23:G23"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="E21:G21"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B14:C14"/>
@@ -2273,9 +2405,9 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="E25:G25"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="E24:G24"/>
   </mergeCells>
   <phoneticPr fontId="6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2284,280 +2416,419 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr defaultRowHeight="13.5" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="8" style="19" customWidth="1"/>
-    <col min="2" max="2" width="10" style="19" customWidth="1"/>
-    <col min="3" max="3" width="16.875" style="19" customWidth="1"/>
-    <col min="4" max="4" width="25" style="19" customWidth="1"/>
-    <col min="5" max="5" width="40.625" style="19" customWidth="1"/>
-    <col min="6" max="7" width="10.625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="12" style="20" customWidth="1"/>
-    <col min="9" max="9" width="15" style="20" customWidth="1"/>
-    <col min="10" max="11" width="10.625" style="20" customWidth="1"/>
-    <col min="12" max="13" width="10.625" style="20" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="14" width="20.625" style="19" customWidth="1" collapsed="1"/>
-    <col min="15" max="16" width="12" style="19" customWidth="1"/>
-    <col min="17" max="18" width="10" style="20" customWidth="1"/>
-    <col min="19" max="19" width="8" style="20" customWidth="1"/>
-    <col min="20" max="20" width="15" style="20" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="15" style="19" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="30" style="19" customWidth="1"/>
-    <col min="23" max="23" width="20" style="19" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="24" max="24" width="9" style="19" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="9" style="19" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="19"/>
+    <col min="1" max="1" width="8" style="15" customWidth="1"/>
+    <col min="2" max="2" width="10" style="15" customWidth="1"/>
+    <col min="3" max="3" width="16.875" style="15" customWidth="1"/>
+    <col min="4" max="4" width="25" style="37" customWidth="1"/>
+    <col min="5" max="5" width="40.625" style="37" customWidth="1"/>
+    <col min="6" max="7" width="10.625" style="44" customWidth="1"/>
+    <col min="8" max="8" width="12" style="16" customWidth="1"/>
+    <col min="9" max="9" width="15" style="16" customWidth="1"/>
+    <col min="10" max="11" width="10.625" style="16" customWidth="1"/>
+    <col min="12" max="13" width="10.625" style="16" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="20.625" style="15" customWidth="1" collapsed="1"/>
+    <col min="15" max="16" width="12" style="15" customWidth="1"/>
+    <col min="17" max="18" width="10" style="16" customWidth="1"/>
+    <col min="19" max="19" width="8" style="16" customWidth="1"/>
+    <col min="20" max="20" width="15" style="16" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="15" style="15" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="30" style="15" customWidth="1"/>
+    <col min="23" max="23" width="20" style="15" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="9" customWidth="1" collapsed="1"/>
+    <col min="25" max="25" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G2" s="21"/>
-    </row>
-    <row r="3" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="6" t="s">
+      <c r="G2" s="45"/>
+    </row>
+    <row r="3" spans="1:23" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="R3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="U3" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="V3" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="W3" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="B4" s="26" t="s">
+    <row r="4" spans="1:23" ht="42.75" x14ac:dyDescent="0.15">
+      <c r="A4" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="B4" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="H4" s="55"/>
+      <c r="I4" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="J4" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="P4" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="35">
+        <v>80</v>
+      </c>
+      <c r="T4" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="U4" s="35"/>
+      <c r="V4" s="35"/>
+      <c r="W4" s="35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="42"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="I5" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="J4" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="P4" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26">
+      <c r="J5" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="P5" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q5" s="42"/>
+      <c r="R5" s="42"/>
+      <c r="S5" s="42">
         <v>80</v>
       </c>
-      <c r="T4" s="26" t="s">
+      <c r="T5" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="U4" s="27"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="29" t="s">
-        <v>264</v>
-      </c>
-      <c r="B5" s="29" t="s">
+      <c r="U5" s="42"/>
+      <c r="V5" s="42"/>
+      <c r="W5" s="42" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="A6" s="36" t="s">
+        <v>270</v>
+      </c>
+      <c r="B6" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C6" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D6" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E6" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F6" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G6" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H6" s="57"/>
+      <c r="I6" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="J6" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="P6" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36">
+        <v>80</v>
+      </c>
+      <c r="T6" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="U6" s="36"/>
+      <c r="V6" s="36"/>
+      <c r="W6" s="36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="42"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="F7" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="H7" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I7" s="56" t="s">
         <v>84</v>
       </c>
-      <c r="J5" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="P5" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29">
+      <c r="J7" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="P7" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="42"/>
+      <c r="S7" s="42">
         <v>80</v>
       </c>
-      <c r="T5" s="29" t="s">
+      <c r="T7" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="U5" s="30"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A6" s="41" t="s">
-        <v>261</v>
-      </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="41"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="42"/>
-      <c r="V6" s="42"/>
-      <c r="W6" s="30"/>
-    </row>
-    <row r="7" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="25"/>
-      <c r="P7" s="25"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
-      <c r="T7" s="23"/>
-      <c r="U7" s="24"/>
-      <c r="V7" s="24"/>
-      <c r="W7" s="24"/>
+      <c r="U7" s="42"/>
+      <c r="V7" s="42"/>
+      <c r="W7" s="42" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="41" t="s">
+        <v>271</v>
+      </c>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="41"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="41"/>
+      <c r="Q8" s="41"/>
+      <c r="R8" s="41"/>
+      <c r="S8" s="41"/>
+      <c r="T8" s="41"/>
+      <c r="U8" s="41"/>
+      <c r="V8" s="41"/>
+      <c r="W8" s="41"/>
+    </row>
+    <row r="9" spans="1:23" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="42"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="42"/>
+      <c r="O9" s="42"/>
+      <c r="P9" s="42"/>
+      <c r="Q9" s="42"/>
+      <c r="R9" s="42"/>
+      <c r="S9" s="42"/>
+      <c r="T9" s="42"/>
+      <c r="U9" s="42"/>
+      <c r="V9" s="42"/>
+      <c r="W9" s="42"/>
+    </row>
+    <row r="10" spans="1:23" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="43" t="s">
+        <v>272</v>
+      </c>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="43"/>
+    </row>
+    <row r="11" spans="1:23" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="42"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="42"/>
+      <c r="O11" s="42"/>
+      <c r="P11" s="42"/>
+      <c r="Q11" s="42"/>
+      <c r="R11" s="42"/>
+      <c r="S11" s="42"/>
+      <c r="T11" s="42"/>
+      <c r="U11" s="42"/>
+      <c r="V11" s="42"/>
+      <c r="W11" s="42"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:W3" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <phoneticPr fontId="6"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="U4:U7" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="U5:U11" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"〇,×,保留"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2567,410 +2838,383 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:X9"/>
+  <dimension ref="A1:X8"/>
   <sheetFormatPr defaultRowHeight="13.5" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="8" style="19" customWidth="1"/>
-    <col min="2" max="2" width="10" style="19" customWidth="1"/>
-    <col min="3" max="3" width="16.875" style="19" customWidth="1"/>
-    <col min="4" max="4" width="25" style="19" customWidth="1"/>
-    <col min="5" max="5" width="40.625" style="19" customWidth="1"/>
-    <col min="6" max="7" width="10.625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="12" style="20" customWidth="1"/>
-    <col min="9" max="9" width="15" style="20" customWidth="1"/>
-    <col min="10" max="11" width="10.625" style="20" customWidth="1"/>
-    <col min="12" max="13" width="10.625" style="20" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="14" width="20.625" style="19" customWidth="1" collapsed="1"/>
-    <col min="15" max="16" width="12" style="19" customWidth="1"/>
-    <col min="17" max="18" width="10" style="20" customWidth="1"/>
-    <col min="19" max="19" width="8" style="20" customWidth="1"/>
-    <col min="20" max="20" width="15" style="20" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="15" style="19" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="30" style="19" customWidth="1"/>
-    <col min="23" max="23" width="20" style="19" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="24" max="24" width="9" style="19" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="9" style="19" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="19"/>
+    <col min="1" max="1" width="8" style="15" customWidth="1"/>
+    <col min="2" max="2" width="10" style="15" customWidth="1"/>
+    <col min="3" max="3" width="16.875" style="15" customWidth="1"/>
+    <col min="4" max="4" width="25" style="15" customWidth="1"/>
+    <col min="5" max="5" width="40.625" style="15" customWidth="1"/>
+    <col min="6" max="7" width="10.625" style="16" customWidth="1"/>
+    <col min="8" max="8" width="12" style="16" customWidth="1"/>
+    <col min="9" max="9" width="15" style="16" customWidth="1"/>
+    <col min="10" max="11" width="10.625" style="16" customWidth="1"/>
+    <col min="12" max="13" width="10.625" style="16" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="20.625" style="15" customWidth="1" collapsed="1"/>
+    <col min="15" max="16" width="12" style="15" customWidth="1"/>
+    <col min="17" max="18" width="10" style="16" customWidth="1"/>
+    <col min="19" max="19" width="8" style="16" customWidth="1"/>
+    <col min="20" max="20" width="15" style="16" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="15" style="15" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="30" style="15" customWidth="1"/>
+    <col min="23" max="23" width="20" style="15" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="9" style="15" customWidth="1" collapsed="1"/>
+    <col min="25" max="25" width="9" style="15" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G2" s="21"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="R3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="U3" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="V3" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="W3" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="B4" s="26" t="s">
+      <c r="A4" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="H4" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="I4" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="J4" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="P4" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26">
+      <c r="J4" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="P4" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22">
         <v>80</v>
       </c>
-      <c r="T4" s="26" t="s">
+      <c r="T4" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="U4" s="27"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="27" t="s">
+      <c r="U4" s="23"/>
+      <c r="V4" s="23"/>
+      <c r="W4" s="23" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="29" t="s">
-        <v>264</v>
-      </c>
-      <c r="B5" s="29" t="s">
+      <c r="A5" s="25" t="s">
+        <v>270</v>
+      </c>
+      <c r="B5" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H5" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="J5" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="P5" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29">
+      <c r="J5" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="P5" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25">
         <v>90</v>
       </c>
-      <c r="T5" s="29" t="s">
+      <c r="T5" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="U5" s="30"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30" t="s">
+      <c r="U5" s="26"/>
+      <c r="V5" s="26"/>
+      <c r="W5" s="26" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="29" t="s">
-        <v>264</v>
-      </c>
-      <c r="B6" s="29" t="s">
+      <c r="A6" s="25" t="s">
+        <v>270</v>
+      </c>
+      <c r="B6" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="G6" s="29" t="s">
+      <c r="G6" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="H6" s="29" t="s">
+      <c r="H6" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="I6" s="29" t="s">
+      <c r="I6" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="J6" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="P6" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="29"/>
-      <c r="S6" s="29">
+      <c r="J6" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="P6" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25">
         <v>80</v>
       </c>
-      <c r="T6" s="29" t="s">
+      <c r="T6" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="U6" s="30"/>
-      <c r="V6" s="30"/>
-      <c r="W6" s="30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A7" s="41" t="s">
-        <v>261</v>
-      </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="43"/>
-      <c r="P7" s="43"/>
-      <c r="Q7" s="41"/>
-      <c r="R7" s="41"/>
-      <c r="S7" s="41"/>
-      <c r="T7" s="41"/>
-      <c r="U7" s="42"/>
-      <c r="V7" s="42"/>
-      <c r="W7" s="30"/>
+      <c r="U6" s="26"/>
+      <c r="V6" s="26"/>
+      <c r="W6" s="26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="P7" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19">
+        <v>60</v>
+      </c>
+      <c r="T7" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="8" spans="1:23" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="F8" s="23" t="s">
+      <c r="A8" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F8" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="G8" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="H8" s="23" t="s">
+      <c r="G8" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="I8" s="23" t="s">
+      <c r="I8" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="J8" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="P8" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23">
-        <v>60</v>
-      </c>
-      <c r="T8" s="23" t="s">
+      <c r="J8" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="P8" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19"/>
+      <c r="S8" s="19">
+        <v>70</v>
+      </c>
+      <c r="T8" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="U8" s="24"/>
-      <c r="V8" s="24"/>
-      <c r="W8" s="24" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="E9" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="J9" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="P9" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23">
-        <v>70</v>
-      </c>
-      <c r="T9" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="U9" s="24"/>
-      <c r="V9" s="24"/>
-      <c r="W9" s="24" t="s">
+      <c r="U8" s="20"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2978,7 +3222,7 @@
   <autoFilter ref="A3:W3" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <phoneticPr fontId="6"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="U4:U9" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="U4:U8" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"〇,×,保留"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2988,300 +3232,273 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:X6"/>
   <sheetFormatPr defaultRowHeight="13.5" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="8" style="19" customWidth="1"/>
-    <col min="2" max="2" width="10" style="19" customWidth="1"/>
-    <col min="3" max="3" width="16.875" style="19" customWidth="1"/>
-    <col min="4" max="4" width="25" style="19" customWidth="1"/>
-    <col min="5" max="5" width="40.625" style="19" customWidth="1"/>
-    <col min="6" max="7" width="10.625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="12" style="20" customWidth="1"/>
-    <col min="9" max="9" width="15" style="20" customWidth="1"/>
-    <col min="10" max="11" width="10.625" style="20" customWidth="1"/>
-    <col min="12" max="13" width="10.625" style="20" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="14" width="20.625" style="19" customWidth="1" collapsed="1"/>
-    <col min="15" max="16" width="12" style="19" customWidth="1"/>
-    <col min="17" max="18" width="10" style="20" customWidth="1"/>
-    <col min="19" max="19" width="8" style="20" customWidth="1"/>
-    <col min="20" max="20" width="15" style="20" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="15" style="19" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="30" style="19" customWidth="1"/>
-    <col min="23" max="23" width="20" style="19" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="24" max="24" width="9" style="19" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="9" style="19" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="19"/>
+    <col min="1" max="1" width="8" style="15" customWidth="1"/>
+    <col min="2" max="2" width="10" style="15" customWidth="1"/>
+    <col min="3" max="3" width="16.875" style="15" customWidth="1"/>
+    <col min="4" max="4" width="25" style="15" customWidth="1"/>
+    <col min="5" max="5" width="40.625" style="15" customWidth="1"/>
+    <col min="6" max="7" width="10.625" style="16" customWidth="1"/>
+    <col min="8" max="8" width="12" style="16" customWidth="1"/>
+    <col min="9" max="9" width="15" style="16" customWidth="1"/>
+    <col min="10" max="11" width="10.625" style="16" customWidth="1"/>
+    <col min="12" max="13" width="10.625" style="16" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="20.625" style="15" customWidth="1" collapsed="1"/>
+    <col min="15" max="16" width="12" style="15" customWidth="1"/>
+    <col min="17" max="18" width="10" style="16" customWidth="1"/>
+    <col min="19" max="19" width="8" style="16" customWidth="1"/>
+    <col min="20" max="20" width="15" style="16" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="15" style="15" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="30" style="15" customWidth="1"/>
+    <col min="23" max="23" width="20" style="15" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="9" style="15" customWidth="1" collapsed="1"/>
+    <col min="25" max="25" width="9" style="15" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G2" s="21"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="R3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="U3" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="V3" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="W3" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="B4" s="26" t="s">
+      <c r="A4" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="H4" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="I4" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="J4" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="P4" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26">
+      <c r="J4" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="P4" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22">
         <v>80</v>
       </c>
-      <c r="T4" s="26" t="s">
+      <c r="T4" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="U4" s="27"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="27" t="s">
+      <c r="U4" s="23"/>
+      <c r="V4" s="23"/>
+      <c r="W4" s="23" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="29" t="s">
-        <v>264</v>
-      </c>
-      <c r="B5" s="29" t="s">
+      <c r="A5" s="25" t="s">
+        <v>270</v>
+      </c>
+      <c r="B5" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H5" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="P5" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29">
+      <c r="J5" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="P5" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25">
         <v>80</v>
       </c>
-      <c r="T5" s="29" t="s">
+      <c r="T5" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="U5" s="30"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A6" s="41" t="s">
-        <v>261</v>
-      </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="41"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="42"/>
-      <c r="V6" s="42"/>
-      <c r="W6" s="30"/>
-    </row>
-    <row r="7" spans="1:23" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="B7" s="23" t="s">
+      <c r="U5" s="26"/>
+      <c r="V5" s="26"/>
+      <c r="W5" s="26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="B6" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C6" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D6" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E6" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F6" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G6" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H6" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="I7" s="23" t="s">
+      <c r="I6" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="J7" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="P7" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23">
+      <c r="J6" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="P6" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19">
         <v>80</v>
       </c>
-      <c r="T7" s="23" t="s">
+      <c r="T6" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="U7" s="24"/>
-      <c r="V7" s="24"/>
-      <c r="W7" s="24" t="s">
+      <c r="U6" s="20"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3289,7 +3506,7 @@
   <autoFilter ref="A3:W3" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <phoneticPr fontId="6"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="U4:U7" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="U4:U6" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"〇,×,保留"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3299,300 +3516,273 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:X6"/>
   <sheetFormatPr defaultRowHeight="13.5" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="8" style="19" customWidth="1"/>
-    <col min="2" max="2" width="10" style="19" customWidth="1"/>
-    <col min="3" max="3" width="16.875" style="19" customWidth="1"/>
-    <col min="4" max="4" width="25" style="19" customWidth="1"/>
-    <col min="5" max="5" width="40.625" style="19" customWidth="1"/>
-    <col min="6" max="7" width="10.625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="12" style="20" customWidth="1"/>
-    <col min="9" max="9" width="15" style="20" customWidth="1"/>
-    <col min="10" max="11" width="10.625" style="20" customWidth="1"/>
-    <col min="12" max="13" width="10.625" style="20" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="14" width="20.625" style="19" customWidth="1" collapsed="1"/>
-    <col min="15" max="16" width="12" style="19" customWidth="1"/>
-    <col min="17" max="18" width="10" style="20" customWidth="1"/>
-    <col min="19" max="19" width="8" style="20" customWidth="1"/>
-    <col min="20" max="20" width="15" style="20" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="15" style="19" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="30" style="19" customWidth="1"/>
-    <col min="23" max="23" width="20" style="19" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="24" max="24" width="9" style="19" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="9" style="19" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="19"/>
+    <col min="1" max="1" width="8" style="15" customWidth="1"/>
+    <col min="2" max="2" width="10" style="15" customWidth="1"/>
+    <col min="3" max="3" width="16.875" style="15" customWidth="1"/>
+    <col min="4" max="4" width="25" style="15" customWidth="1"/>
+    <col min="5" max="5" width="40.625" style="15" customWidth="1"/>
+    <col min="6" max="7" width="10.625" style="16" customWidth="1"/>
+    <col min="8" max="8" width="12" style="16" customWidth="1"/>
+    <col min="9" max="9" width="15" style="16" customWidth="1"/>
+    <col min="10" max="11" width="10.625" style="16" customWidth="1"/>
+    <col min="12" max="13" width="10.625" style="16" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="20.625" style="15" customWidth="1" collapsed="1"/>
+    <col min="15" max="16" width="12" style="15" customWidth="1"/>
+    <col min="17" max="18" width="10" style="16" customWidth="1"/>
+    <col min="19" max="19" width="8" style="16" customWidth="1"/>
+    <col min="20" max="20" width="15" style="16" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="15" style="15" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="30" style="15" customWidth="1"/>
+    <col min="23" max="23" width="20" style="15" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="9" style="15" customWidth="1" collapsed="1"/>
+    <col min="25" max="25" width="9" style="15" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G2" s="21"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="R3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="U3" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="V3" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="W3" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="B4" s="26" t="s">
+      <c r="A4" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="H4" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="I4" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="J4" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="P4" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26">
+      <c r="J4" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="P4" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22">
         <v>80</v>
       </c>
-      <c r="T4" s="26" t="s">
+      <c r="T4" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="U4" s="27"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="27" t="s">
+      <c r="U4" s="23"/>
+      <c r="V4" s="23"/>
+      <c r="W4" s="23" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="29" t="s">
-        <v>264</v>
-      </c>
-      <c r="B5" s="29" t="s">
+      <c r="A5" s="25" t="s">
+        <v>270</v>
+      </c>
+      <c r="B5" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H5" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="J5" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="P5" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29">
+      <c r="J5" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="P5" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25">
         <v>80</v>
       </c>
-      <c r="T5" s="29" t="s">
+      <c r="T5" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="U5" s="30"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A6" s="41" t="s">
-        <v>261</v>
-      </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="41"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="42"/>
-      <c r="V6" s="42"/>
-      <c r="W6" s="30"/>
-    </row>
-    <row r="7" spans="1:23" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="B7" s="23" t="s">
+      <c r="U5" s="26"/>
+      <c r="V5" s="26"/>
+      <c r="W5" s="26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="B6" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C6" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D6" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E6" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F6" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G6" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H6" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="I7" s="23" t="s">
+      <c r="I6" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="J7" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="P7" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23">
+      <c r="J6" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="P6" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19">
         <v>65</v>
       </c>
-      <c r="T7" s="23" t="s">
+      <c r="T6" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="U7" s="24"/>
-      <c r="V7" s="24"/>
-      <c r="W7" s="24" t="s">
+      <c r="U6" s="20"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3600,7 +3790,7 @@
   <autoFilter ref="A3:W3" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <phoneticPr fontId="6"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="U4:U7" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="U4:U6" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"〇,×,保留"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3610,300 +3800,273 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:X6"/>
   <sheetFormatPr defaultRowHeight="13.5" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="8" style="19" customWidth="1"/>
-    <col min="2" max="2" width="10" style="19" customWidth="1"/>
-    <col min="3" max="3" width="16.875" style="19" customWidth="1"/>
-    <col min="4" max="4" width="25" style="19" customWidth="1"/>
-    <col min="5" max="5" width="40.625" style="19" customWidth="1"/>
-    <col min="6" max="7" width="10.625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="12" style="20" customWidth="1"/>
-    <col min="9" max="9" width="15" style="20" customWidth="1"/>
-    <col min="10" max="11" width="10.625" style="20" customWidth="1"/>
-    <col min="12" max="13" width="10.625" style="20" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="14" width="20.625" style="19" customWidth="1" collapsed="1"/>
-    <col min="15" max="16" width="12" style="19" customWidth="1"/>
-    <col min="17" max="18" width="10" style="20" customWidth="1"/>
-    <col min="19" max="19" width="8" style="20" customWidth="1"/>
-    <col min="20" max="20" width="15" style="20" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="15" style="19" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="30" style="19" customWidth="1"/>
-    <col min="23" max="23" width="20" style="19" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="24" max="24" width="9" style="19" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="9" style="19" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="19"/>
+    <col min="1" max="1" width="8" style="15" customWidth="1"/>
+    <col min="2" max="2" width="10" style="15" customWidth="1"/>
+    <col min="3" max="3" width="16.875" style="15" customWidth="1"/>
+    <col min="4" max="4" width="25" style="15" customWidth="1"/>
+    <col min="5" max="5" width="40.625" style="15" customWidth="1"/>
+    <col min="6" max="7" width="10.625" style="16" customWidth="1"/>
+    <col min="8" max="8" width="12" style="16" customWidth="1"/>
+    <col min="9" max="9" width="15" style="16" customWidth="1"/>
+    <col min="10" max="11" width="10.625" style="16" customWidth="1"/>
+    <col min="12" max="13" width="10.625" style="16" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="20.625" style="15" customWidth="1" collapsed="1"/>
+    <col min="15" max="16" width="12" style="15" customWidth="1"/>
+    <col min="17" max="18" width="10" style="16" customWidth="1"/>
+    <col min="19" max="19" width="8" style="16" customWidth="1"/>
+    <col min="20" max="20" width="15" style="16" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="15" style="15" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="30" style="15" customWidth="1"/>
+    <col min="23" max="23" width="20" style="15" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="9" style="15" customWidth="1" collapsed="1"/>
+    <col min="25" max="25" width="9" style="15" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G2" s="21"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="R3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="U3" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="V3" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="W3" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="B4" s="26" t="s">
+      <c r="A4" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="H4" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="I4" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="J4" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="P4" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26">
+      <c r="J4" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="P4" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22">
         <v>80</v>
       </c>
-      <c r="T4" s="26" t="s">
+      <c r="T4" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="U4" s="27"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="27" t="s">
+      <c r="U4" s="23"/>
+      <c r="V4" s="23"/>
+      <c r="W4" s="23" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="29" t="s">
-        <v>264</v>
-      </c>
-      <c r="B5" s="29" t="s">
+      <c r="A5" s="25" t="s">
+        <v>270</v>
+      </c>
+      <c r="B5" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H5" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="J5" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="P5" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29">
+      <c r="J5" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="P5" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25">
         <v>55</v>
       </c>
-      <c r="T5" s="29" t="s">
+      <c r="T5" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="U5" s="30"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A6" s="41" t="s">
-        <v>261</v>
-      </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="41"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="42"/>
-      <c r="V6" s="42"/>
-      <c r="W6" s="30"/>
-    </row>
-    <row r="7" spans="1:23" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="B7" s="23" t="s">
+      <c r="U5" s="26"/>
+      <c r="V5" s="26"/>
+      <c r="W5" s="26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="B6" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="24" t="s">
+      <c r="C6" s="19"/>
+      <c r="D6" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E6" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F6" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G6" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H6" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="I7" s="23" t="s">
+      <c r="I6" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="J7" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="P7" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23">
+      <c r="J6" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="P6" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19">
         <v>60</v>
       </c>
-      <c r="T7" s="23" t="s">
+      <c r="T6" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="U7" s="24"/>
-      <c r="V7" s="24"/>
-      <c r="W7" s="24" t="s">
+      <c r="U6" s="20"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3911,7 +4074,7 @@
   <autoFilter ref="A3:W3" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <phoneticPr fontId="6"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="U4:U7" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="U4:U6" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"〇,×,保留"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3921,280 +4084,253 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:X6"/>
   <sheetFormatPr defaultRowHeight="13.5" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="8" style="19" customWidth="1"/>
-    <col min="2" max="2" width="10" style="19" customWidth="1"/>
-    <col min="3" max="3" width="16.875" style="19" customWidth="1"/>
-    <col min="4" max="4" width="25" style="19" customWidth="1"/>
-    <col min="5" max="5" width="40.625" style="19" customWidth="1"/>
-    <col min="6" max="7" width="10.625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="12" style="20" customWidth="1"/>
-    <col min="9" max="9" width="15" style="20" customWidth="1"/>
-    <col min="10" max="11" width="10.625" style="20" customWidth="1"/>
-    <col min="12" max="13" width="10.625" style="20" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="14" width="20.625" style="19" customWidth="1" collapsed="1"/>
-    <col min="15" max="16" width="12" style="19" customWidth="1"/>
-    <col min="17" max="18" width="10" style="20" customWidth="1"/>
-    <col min="19" max="19" width="8" style="20" customWidth="1"/>
-    <col min="20" max="20" width="15" style="20" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="15" style="19" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="30" style="19" customWidth="1"/>
-    <col min="23" max="23" width="20" style="19" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="24" max="24" width="9" style="19" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="9" style="19" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="19"/>
+    <col min="1" max="1" width="8" style="15" customWidth="1"/>
+    <col min="2" max="2" width="10" style="15" customWidth="1"/>
+    <col min="3" max="3" width="16.875" style="15" customWidth="1"/>
+    <col min="4" max="4" width="25" style="15" customWidth="1"/>
+    <col min="5" max="5" width="40.625" style="15" customWidth="1"/>
+    <col min="6" max="7" width="10.625" style="16" customWidth="1"/>
+    <col min="8" max="8" width="12" style="16" customWidth="1"/>
+    <col min="9" max="9" width="15" style="16" customWidth="1"/>
+    <col min="10" max="11" width="10.625" style="16" customWidth="1"/>
+    <col min="12" max="13" width="10.625" style="16" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="20.625" style="15" customWidth="1" collapsed="1"/>
+    <col min="15" max="16" width="12" style="15" customWidth="1"/>
+    <col min="17" max="18" width="10" style="16" customWidth="1"/>
+    <col min="19" max="19" width="8" style="16" customWidth="1"/>
+    <col min="20" max="20" width="15" style="16" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="15" style="15" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="30" style="15" customWidth="1"/>
+    <col min="23" max="23" width="20" style="15" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="9" style="15" customWidth="1" collapsed="1"/>
+    <col min="25" max="25" width="9" style="15" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G2" s="21"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="R3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="U3" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="V3" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="W3" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="B4" s="26" t="s">
+      <c r="A4" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="H4" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="I4" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="J4" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="P4" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26">
+      <c r="J4" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="P4" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22">
         <v>80</v>
       </c>
-      <c r="T4" s="26" t="s">
+      <c r="T4" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="U4" s="27"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="27" t="s">
+      <c r="U4" s="23"/>
+      <c r="V4" s="23"/>
+      <c r="W4" s="23" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="29" t="s">
-        <v>264</v>
-      </c>
-      <c r="B5" s="29" t="s">
+      <c r="A5" s="25" t="s">
+        <v>270</v>
+      </c>
+      <c r="B5" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H5" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="J5" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="P5" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29">
+      <c r="J5" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="P5" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25">
         <v>80</v>
       </c>
-      <c r="T5" s="29" t="s">
+      <c r="T5" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="U5" s="30"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A6" s="41" t="s">
-        <v>261</v>
-      </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="41"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="42"/>
-      <c r="V6" s="42"/>
-      <c r="W6" s="30"/>
-    </row>
-    <row r="7" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="25"/>
-      <c r="P7" s="25"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
-      <c r="T7" s="23"/>
-      <c r="U7" s="24"/>
-      <c r="V7" s="24"/>
-      <c r="W7" s="24"/>
+      <c r="U5" s="26"/>
+      <c r="V5" s="26"/>
+      <c r="W5" s="26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="21"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:W3" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <phoneticPr fontId="6"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="U4:U7" xr:uid="{00000000-0002-0000-0600-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="U4:U6" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>"〇,×,保留"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4203,225 +4339,332 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89F07216-4932-4252-AF22-8E4517B4BE5D}">
-  <dimension ref="A1:X7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{393E5711-F722-463B-B7B7-FA9FBBE5F884}">
+  <dimension ref="A1:X11"/>
   <sheetFormatPr defaultRowHeight="13.5" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="8" style="19" customWidth="1"/>
-    <col min="2" max="2" width="10" style="19" customWidth="1"/>
-    <col min="3" max="3" width="16.875" style="19" customWidth="1"/>
-    <col min="4" max="4" width="25" style="19" customWidth="1"/>
-    <col min="5" max="5" width="40.625" style="19" customWidth="1"/>
-    <col min="6" max="7" width="10.625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="12" style="20" customWidth="1"/>
-    <col min="9" max="9" width="15" style="20" customWidth="1"/>
-    <col min="10" max="11" width="10.625" style="20" customWidth="1"/>
-    <col min="12" max="13" width="10.625" style="20" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="14" width="20.625" style="19" customWidth="1" collapsed="1"/>
-    <col min="15" max="16" width="12" style="19" customWidth="1"/>
-    <col min="17" max="18" width="10" style="20" customWidth="1"/>
-    <col min="19" max="19" width="8" style="20" customWidth="1"/>
-    <col min="20" max="20" width="15" style="20" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="15" style="19" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="30" style="19" customWidth="1"/>
-    <col min="23" max="23" width="20" style="19" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="24" max="24" width="9" style="19" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="9" style="19" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="19"/>
+    <col min="1" max="1" width="8" style="15" customWidth="1"/>
+    <col min="2" max="2" width="10" style="15" customWidth="1"/>
+    <col min="3" max="3" width="16.875" style="15" customWidth="1"/>
+    <col min="4" max="4" width="25" style="37" customWidth="1"/>
+    <col min="5" max="5" width="40.625" style="37" customWidth="1"/>
+    <col min="6" max="7" width="10.625" style="44" customWidth="1"/>
+    <col min="8" max="8" width="12" style="16" customWidth="1"/>
+    <col min="9" max="9" width="15" style="16" customWidth="1"/>
+    <col min="10" max="11" width="10.625" style="16" customWidth="1"/>
+    <col min="12" max="13" width="10.625" style="16" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="20.625" style="15" customWidth="1" collapsed="1"/>
+    <col min="15" max="16" width="12" style="15" customWidth="1"/>
+    <col min="17" max="18" width="10" style="16" customWidth="1"/>
+    <col min="19" max="19" width="8" style="16" customWidth="1"/>
+    <col min="20" max="20" width="15" style="16" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="15" style="15" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="30" style="15" customWidth="1"/>
+    <col min="23" max="23" width="20" style="15" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="9" customWidth="1" collapsed="1"/>
+    <col min="25" max="25" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="7" t="s">
-        <v>256</v>
+      <c r="A1" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G2" s="21"/>
-    </row>
-    <row r="3" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="6" t="s">
+      <c r="G2" s="45"/>
+    </row>
+    <row r="3" spans="1:23" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="R3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="U3" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="V3" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="W3" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A4" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26"/>
-      <c r="T4" s="26"/>
-      <c r="U4" s="27"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="27"/>
-    </row>
-    <row r="5" spans="1:23" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A5" s="29" t="s">
-        <v>264</v>
-      </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="31"/>
-      <c r="P5" s="31"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="30"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30"/>
+      <c r="A4" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="35"/>
+      <c r="T4" s="35"/>
+      <c r="U4" s="35"/>
+      <c r="V4" s="35"/>
+      <c r="W4" s="35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="42"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42"/>
+      <c r="P5" s="42"/>
+      <c r="Q5" s="42"/>
+      <c r="R5" s="42"/>
+      <c r="S5" s="42"/>
+      <c r="T5" s="42"/>
+      <c r="U5" s="42"/>
+      <c r="V5" s="42"/>
+      <c r="W5" s="42" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="6" spans="1:23" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A6" s="41" t="s">
-        <v>261</v>
-      </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="41"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="42"/>
-      <c r="V6" s="42"/>
-      <c r="W6" s="30"/>
-    </row>
-    <row r="7" spans="1:23" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A7" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="25"/>
-      <c r="P7" s="25"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
-      <c r="T7" s="23"/>
-      <c r="U7" s="24"/>
-      <c r="V7" s="24"/>
-      <c r="W7" s="24"/>
+      <c r="A6" s="36" t="s">
+        <v>270</v>
+      </c>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="36"/>
+      <c r="V6" s="36"/>
+      <c r="W6" s="36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="42"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="42"/>
+      <c r="S7" s="42"/>
+      <c r="T7" s="42"/>
+      <c r="U7" s="42"/>
+      <c r="V7" s="42"/>
+      <c r="W7" s="42" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="41" t="s">
+        <v>271</v>
+      </c>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="41"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="41"/>
+      <c r="Q8" s="41"/>
+      <c r="R8" s="41"/>
+      <c r="S8" s="41"/>
+      <c r="T8" s="41"/>
+      <c r="U8" s="41"/>
+      <c r="V8" s="41"/>
+      <c r="W8" s="41"/>
+    </row>
+    <row r="9" spans="1:23" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="42"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="42"/>
+      <c r="O9" s="42"/>
+      <c r="P9" s="42"/>
+      <c r="Q9" s="42"/>
+      <c r="R9" s="42"/>
+      <c r="S9" s="42"/>
+      <c r="T9" s="42"/>
+      <c r="U9" s="42"/>
+      <c r="V9" s="42"/>
+      <c r="W9" s="42"/>
+    </row>
+    <row r="10" spans="1:23" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="43" t="s">
+        <v>272</v>
+      </c>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="43"/>
+    </row>
+    <row r="11" spans="1:23" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="42"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="42"/>
+      <c r="O11" s="42"/>
+      <c r="P11" s="42"/>
+      <c r="Q11" s="42"/>
+      <c r="R11" s="42"/>
+      <c r="S11" s="42"/>
+      <c r="T11" s="42"/>
+      <c r="U11" s="42"/>
+      <c r="V11" s="42"/>
+      <c r="W11" s="42"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:W3" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
+  <autoFilter ref="A3:W3" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <phoneticPr fontId="6"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="U4:U7" xr:uid="{DE435B7E-078B-437C-BC93-D022748ABD8D}">
+    <dataValidation type="list" allowBlank="1" sqref="U5:U11" xr:uid="{77310BAB-D659-4FCA-B0D2-4A1309572073}">
       <formula1>"〇,×,保留"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4434,984 +4677,984 @@
   <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="32" customWidth="1"/>
-    <col min="2" max="2" width="17.25" style="32" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="32" customWidth="1"/>
-    <col min="4" max="4" width="35.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5" style="32" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="32" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.875" style="32" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="32" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" style="32" customWidth="1"/>
-    <col min="10" max="10" width="14.875" style="32" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.25" style="32" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11" style="32" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="45.375" style="32" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9" style="32" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="32"/>
+    <col min="1" max="1" width="9" style="28" customWidth="1"/>
+    <col min="2" max="2" width="17.25" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="28" customWidth="1"/>
+    <col min="4" max="4" width="35.5" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5" style="28" customWidth="1"/>
+    <col min="6" max="6" width="13.625" style="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.875" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="28" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="28" customWidth="1"/>
+    <col min="10" max="10" width="14.875" style="28" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.25" style="28" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" style="28" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="45.375" style="28" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9" style="28" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="G1" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="32" t="s">
+      <c r="J1" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="L1" s="32" t="s">
+      <c r="L1" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="M1" s="32" t="s">
+      <c r="M1" s="28" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="H2" s="32" t="str">
+      <c r="H2" s="28" t="str">
         <f t="shared" ref="H2:H37" si="0">VLOOKUP(G2,$J$11:$K$15,2,0)</f>
         <v>逆の可能性あり</v>
       </c>
-      <c r="J2" s="32" t="s">
+      <c r="J2" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="K2" s="32" t="s">
+      <c r="K2" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="L2" s="32" t="s">
+      <c r="L2" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="M2" s="32" t="s">
+      <c r="M2" s="28" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F3" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H3" s="32" t="str">
+      <c r="H3" s="28" t="str">
         <f t="shared" si="0"/>
         <v>明確な誤り</v>
       </c>
-      <c r="J3" s="32" t="s">
+      <c r="J3" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="32" t="s">
+      <c r="K3" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="L3" s="32" t="s">
+      <c r="L3" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="M3" s="32" t="s">
+      <c r="M3" s="28" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="F4" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H4" s="32" t="str">
+      <c r="H4" s="28" t="str">
         <f t="shared" si="0"/>
         <v>明確な誤り</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="J4" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="K4" s="32" t="s">
+      <c r="K4" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="L4" s="32" t="s">
+      <c r="L4" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="M4" s="32" t="s">
+      <c r="M4" s="28" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H5" s="32" t="str">
+      <c r="H5" s="28" t="str">
         <f t="shared" si="0"/>
         <v>明確な誤り</v>
       </c>
-      <c r="J5" s="32" t="s">
+      <c r="J5" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="K5" s="32" t="s">
+      <c r="K5" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="L5" s="32" t="s">
+      <c r="L5" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="M5" s="32" t="s">
+      <c r="M5" s="28" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="F6" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="32" t="str">
+      <c r="H6" s="28" t="str">
         <f t="shared" si="0"/>
         <v>明確な誤り</v>
       </c>
-      <c r="J6" s="32" t="s">
+      <c r="J6" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="K6" s="32" t="s">
+      <c r="K6" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="L6" s="32" t="s">
+      <c r="L6" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="M6" s="32" t="s">
+      <c r="M6" s="28" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F7" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H7" s="32" t="str">
+      <c r="H7" s="28" t="str">
         <f t="shared" si="0"/>
         <v>明確な誤り</v>
       </c>
-      <c r="J7" s="32" t="s">
+      <c r="J7" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K7" s="32" t="s">
+      <c r="K7" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="L7" s="32" t="s">
+      <c r="L7" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="M7" s="32" t="s">
+      <c r="M7" s="28" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="28" t="s">
         <v>189</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="F8" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="32" t="str">
+      <c r="H8" s="28" t="str">
         <f t="shared" si="0"/>
         <v>明確な誤り</v>
       </c>
-      <c r="J8" s="32" t="s">
+      <c r="J8" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="K8" s="32" t="s">
+      <c r="K8" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="L8" s="32" t="s">
+      <c r="L8" s="28" t="s">
         <v>190</v>
       </c>
-      <c r="M8" s="32" t="s">
+      <c r="M8" s="28" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="28" t="s">
         <v>192</v>
       </c>
-      <c r="E9" s="32" t="s">
+      <c r="E9" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="F9" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H9" s="32" t="str">
+      <c r="H9" s="28" t="str">
         <f t="shared" si="0"/>
         <v>明確な誤り</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="D10" s="32" t="s">
-        <v>271</v>
-      </c>
-      <c r="E10" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="F10" s="32" t="s">
+      <c r="D10" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="F10" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="H10" s="32" t="str">
+      <c r="H10" s="28" t="str">
         <f t="shared" si="0"/>
         <v>判断が必要</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="D11" s="32" t="s">
-        <v>194</v>
-      </c>
-      <c r="E11" s="32" t="s">
-        <v>195</v>
-      </c>
-      <c r="F11" s="32" t="s">
+      <c r="D11" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="F11" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="G11" s="32" t="s">
+      <c r="G11" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="H11" s="32" t="str">
+      <c r="H11" s="28" t="str">
         <f t="shared" si="0"/>
         <v>逆の可能性あり</v>
       </c>
-      <c r="J11" s="32" t="s">
-        <v>196</v>
-      </c>
-      <c r="K11" s="32" t="s">
-        <v>197</v>
-      </c>
-      <c r="L11" s="32" t="s">
+      <c r="J11" s="28" t="s">
         <v>198</v>
       </c>
+      <c r="K11" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="L11" s="28" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C12" s="32" t="s">
-        <v>199</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>200</v>
-      </c>
-      <c r="E12" s="32" t="s">
+      <c r="C12" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="D12" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="F12" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="G12" s="32" t="s">
+      <c r="G12" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="H12" s="32" t="str">
+      <c r="H12" s="28" t="str">
         <f t="shared" si="0"/>
         <v>逆の可能性あり</v>
       </c>
-      <c r="J12" s="32" t="s">
+      <c r="J12" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="K12" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="L12" s="32" t="s">
-        <v>203</v>
+      <c r="K12" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="L12" s="28" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="D13" s="32" t="s">
-        <v>204</v>
-      </c>
-      <c r="E13" s="32" t="s">
-        <v>205</v>
-      </c>
-      <c r="F13" s="32" t="s">
+      <c r="D13" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="F13" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H13" s="32" t="str">
+      <c r="H13" s="28" t="str">
         <f t="shared" si="0"/>
         <v>明確な誤り</v>
       </c>
-      <c r="J13" s="32" t="s">
+      <c r="J13" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="K13" s="32" t="s">
-        <v>206</v>
-      </c>
-      <c r="L13" s="32" t="s">
-        <v>207</v>
+      <c r="K13" s="28" t="s">
+        <v>208</v>
+      </c>
+      <c r="L13" s="28" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="D14" s="32" t="s">
-        <v>208</v>
-      </c>
-      <c r="E14" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="F14" s="32" t="s">
+      <c r="D14" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="F14" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H14" s="32" t="str">
+      <c r="H14" s="28" t="str">
         <f t="shared" si="0"/>
         <v>明確な誤り</v>
       </c>
-      <c r="J14" s="32" t="s">
+      <c r="J14" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="K14" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="L14" s="32" t="s">
-        <v>211</v>
+      <c r="K14" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="L14" s="28" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="D15" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="E15" s="32" t="s">
-        <v>213</v>
-      </c>
-      <c r="F15" s="32" t="s">
+      <c r="D15" s="28" t="s">
         <v>214</v>
       </c>
-      <c r="G15" s="32" t="s">
+      <c r="E15" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="G15" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="H15" s="32" t="str">
+      <c r="H15" s="28" t="str">
         <f t="shared" si="0"/>
         <v>問題なし</v>
       </c>
-      <c r="J15" s="32" t="s">
+      <c r="J15" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="K15" s="32" t="s">
-        <v>215</v>
-      </c>
-      <c r="L15" s="32" t="s">
-        <v>216</v>
+      <c r="K15" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="L15" s="28" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="D16" s="32" t="s">
-        <v>217</v>
-      </c>
-      <c r="E16" s="32" t="s">
-        <v>218</v>
-      </c>
-      <c r="F16" s="32" t="s">
+      <c r="D16" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="F16" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="G16" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H16" s="32" t="str">
+      <c r="H16" s="28" t="str">
         <f t="shared" si="0"/>
         <v>明確な誤り</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="D17" s="32" t="s">
-        <v>219</v>
-      </c>
-      <c r="E17" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="F17" s="32" t="s">
+      <c r="D17" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="F17" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="G17" s="32" t="s">
+      <c r="G17" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H17" s="32" t="str">
+      <c r="H17" s="28" t="str">
         <f t="shared" si="0"/>
         <v>明確な誤り</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="D18" s="32" t="s">
-        <v>221</v>
-      </c>
-      <c r="E18" s="32" t="s">
-        <v>222</v>
-      </c>
-      <c r="F18" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="G18" s="32" t="s">
+      <c r="D18" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="G18" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="H18" s="32" t="str">
+      <c r="H18" s="28" t="str">
         <f t="shared" si="0"/>
         <v>問題なし</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C19" s="32" t="s">
+      <c r="C19" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="D19" s="32" t="s">
-        <v>223</v>
-      </c>
-      <c r="E19" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="F19" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="G19" s="32" t="s">
+      <c r="D19" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="G19" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="H19" s="32" t="str">
+      <c r="H19" s="28" t="str">
         <f t="shared" si="0"/>
         <v>問題なし</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="D20" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="E20" s="32" t="s">
-        <v>273</v>
-      </c>
-      <c r="F20" s="32" t="s">
+      <c r="D20" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="F20" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="G20" s="32" t="s">
+      <c r="G20" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="H20" s="32" t="str">
+      <c r="H20" s="28" t="str">
         <f t="shared" si="0"/>
         <v>判断が必要</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C21" s="32" t="s">
-        <v>199</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>226</v>
-      </c>
-      <c r="E21" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="F21" s="32" t="s">
+      <c r="C21" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="F21" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="G21" s="32" t="s">
+      <c r="G21" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="H21" s="32" t="str">
+      <c r="H21" s="28" t="str">
         <f t="shared" si="0"/>
         <v>逆の可能性あり</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="32" t="s">
+      <c r="A22" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C22" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="D22" s="32" t="s">
-        <v>228</v>
-      </c>
-      <c r="E22" s="32" t="s">
-        <v>229</v>
-      </c>
-      <c r="F22" s="32" t="s">
+      <c r="D22" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="F22" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="G22" s="32" t="s">
+      <c r="G22" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H22" s="32" t="str">
+      <c r="H22" s="28" t="str">
         <f t="shared" si="0"/>
         <v>明確な誤り</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C23" s="32" t="s">
+      <c r="C23" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="D23" s="32" t="s">
-        <v>230</v>
-      </c>
-      <c r="E23" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="F23" s="32" t="s">
+      <c r="D23" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="F23" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="G23" s="32" t="s">
+      <c r="G23" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H23" s="32" t="str">
+      <c r="H23" s="28" t="str">
         <f t="shared" si="0"/>
         <v>明確な誤り</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C24" s="32" t="s">
+      <c r="C24" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="D24" s="32" t="s">
-        <v>232</v>
-      </c>
-      <c r="E24" s="32" t="s">
-        <v>233</v>
-      </c>
-      <c r="F24" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="G24" s="32" t="s">
+      <c r="D24" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="G24" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="H24" s="32" t="str">
+      <c r="H24" s="28" t="str">
         <f t="shared" si="0"/>
         <v>問題なし</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C25" s="32" t="s">
+      <c r="C25" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="D25" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="E25" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="F25" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="G25" s="32" t="s">
+      <c r="D25" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="G25" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="H25" s="32" t="str">
+      <c r="H25" s="28" t="str">
         <f t="shared" si="0"/>
         <v>問題なし</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="D26" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="E26" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="F26" s="32" t="s">
+      <c r="D26" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="F26" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="G26" s="32" t="s">
+      <c r="G26" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="H26" s="32" t="str">
+      <c r="H26" s="28" t="str">
         <f t="shared" si="0"/>
         <v>判断が必要</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="32" t="s">
+      <c r="B27" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="C27" s="32" t="s">
+      <c r="C27" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="D27" s="32" t="s">
-        <v>238</v>
-      </c>
-      <c r="E27" s="32" t="s">
-        <v>239</v>
-      </c>
-      <c r="F27" s="32" t="s">
+      <c r="D27" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="F27" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="G27" s="32" t="s">
+      <c r="G27" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H27" s="32" t="str">
+      <c r="H27" s="28" t="str">
         <f t="shared" si="0"/>
         <v>明確な誤り</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C28" s="32" t="s">
+      <c r="C28" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="D28" s="32" t="s">
-        <v>240</v>
-      </c>
-      <c r="E28" s="32" t="s">
-        <v>241</v>
-      </c>
-      <c r="F28" s="32" t="s">
+      <c r="D28" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>244</v>
+      </c>
+      <c r="F28" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="G28" s="32" t="s">
+      <c r="G28" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H28" s="32" t="str">
+      <c r="H28" s="28" t="str">
         <f t="shared" si="0"/>
         <v>明確な誤り</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C29" s="32" t="s">
+      <c r="C29" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="D29" s="32" t="s">
-        <v>242</v>
-      </c>
-      <c r="E29" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="F29" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="G29" s="32" t="s">
+      <c r="D29" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="G29" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="H29" s="32" t="str">
+      <c r="H29" s="28" t="str">
         <f t="shared" si="0"/>
         <v>問題なし</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C30" s="32" t="s">
+      <c r="C30" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="D30" s="32" t="s">
-        <v>274</v>
-      </c>
-      <c r="E30" s="32" t="s">
-        <v>275</v>
-      </c>
-      <c r="F30" s="32" t="s">
+      <c r="D30" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="E30" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="F30" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="G30" s="32" t="s">
+      <c r="G30" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="H30" s="32" t="str">
+      <c r="H30" s="28" t="str">
         <f t="shared" si="0"/>
         <v>判断が必要</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C31" s="32" t="s">
+      <c r="C31" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="D31" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="E31" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="F31" s="32" t="s">
+      <c r="D31" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="E31" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="F31" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="G31" s="32" t="s">
+      <c r="G31" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="H31" s="32" t="str">
+      <c r="H31" s="28" t="str">
         <f t="shared" si="0"/>
         <v>判断が必要</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="32" t="s">
+      <c r="A32" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="32" t="s">
+      <c r="B32" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="D32" s="32" t="s">
-        <v>244</v>
-      </c>
-      <c r="E32" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="F32" s="32" t="s">
+      <c r="D32" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="E32" s="28" t="s">
+        <v>252</v>
+      </c>
+      <c r="F32" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="G32" s="32" t="s">
+      <c r="G32" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H32" s="32" t="str">
+      <c r="H32" s="28" t="str">
         <f t="shared" si="0"/>
         <v>明確な誤り</v>
       </c>
     </row>
     <row r="33" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C33" s="32" t="s">
+      <c r="C33" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="D33" s="32" t="s">
-        <v>246</v>
-      </c>
-      <c r="E33" s="32" t="s">
-        <v>247</v>
-      </c>
-      <c r="F33" s="32" t="s">
+      <c r="D33" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="E33" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="F33" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="G33" s="32" t="s">
+      <c r="G33" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H33" s="32" t="str">
+      <c r="H33" s="28" t="str">
         <f t="shared" si="0"/>
         <v>明確な誤り</v>
       </c>
     </row>
     <row r="34" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C34" s="32" t="s">
+      <c r="C34" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="D34" s="32" t="s">
-        <v>248</v>
-      </c>
-      <c r="E34" s="32" t="s">
-        <v>249</v>
-      </c>
-      <c r="F34" s="32" t="s">
+      <c r="D34" s="28" t="s">
+        <v>255</v>
+      </c>
+      <c r="E34" s="28" t="s">
+        <v>256</v>
+      </c>
+      <c r="F34" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="G34" s="32" t="s">
+      <c r="G34" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H34" s="32" t="str">
+      <c r="H34" s="28" t="str">
         <f t="shared" si="0"/>
         <v>明確な誤り</v>
       </c>
     </row>
     <row r="35" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C35" s="32" t="s">
+      <c r="C35" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="D35" s="32" t="s">
-        <v>250</v>
-      </c>
-      <c r="E35" s="32" t="s">
-        <v>251</v>
-      </c>
-      <c r="F35" s="32" t="s">
+      <c r="D35" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="E35" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="F35" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="G35" s="32" t="s">
+      <c r="G35" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H35" s="32" t="str">
+      <c r="H35" s="28" t="str">
         <f t="shared" si="0"/>
         <v>明確な誤り</v>
       </c>
     </row>
     <row r="36" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C36" s="32" t="s">
+      <c r="C36" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="D36" s="32" t="s">
-        <v>252</v>
-      </c>
-      <c r="E36" s="32" t="s">
-        <v>253</v>
-      </c>
-      <c r="F36" s="32" t="s">
+      <c r="D36" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="E36" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="F36" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="G36" s="32" t="s">
+      <c r="G36" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="H36" s="32" t="str">
+      <c r="H36" s="28" t="str">
         <f t="shared" si="0"/>
         <v>逆の可能性あり</v>
       </c>
     </row>
     <row r="37" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C37" s="32" t="s">
-        <v>199</v>
-      </c>
-      <c r="D37" s="32" t="s">
-        <v>254</v>
-      </c>
-      <c r="E37" s="32" t="s">
-        <v>255</v>
-      </c>
-      <c r="F37" s="32" t="s">
+      <c r="C37" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="D37" s="28" t="s">
+        <v>261</v>
+      </c>
+      <c r="E37" s="28" t="s">
+        <v>262</v>
+      </c>
+      <c r="F37" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="G37" s="32" t="s">
+      <c r="G37" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H37" s="32" t="str">
+      <c r="H37" s="28" t="str">
         <f t="shared" si="0"/>
         <v>明確な誤り</v>
       </c>
